--- a/Project Plan.xlsx
+++ b/Project Plan.xlsx
@@ -11,9 +11,30 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="43">
   <si>
     <t>Project Plan</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Calibri, sans-serif"/>
+        <b/>
+        <color rgb="FF000000"/>
+        <sz val="18.0"/>
+      </rPr>
+      <t xml:space="preserve">Project Github link: </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Calibri, sans-serif"/>
+        <b/>
+        <color rgb="FF1155CC"/>
+        <sz val="18.0"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/chaumdh/project-1-submission</t>
+    </r>
   </si>
   <si>
     <t>milestone 1: component and page content added</t>
@@ -146,7 +167,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -159,6 +180,13 @@
       <name val="Calibri"/>
     </font>
     <font/>
+    <font>
+      <b/>
+      <u/>
+      <sz val="18.0"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
     <font>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
@@ -237,7 +265,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -246,30 +274,33 @@
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="2" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -504,504 +535,509 @@
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="4" t="s">
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="4" t="s">
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="S1" s="4"/>
+      <c r="T1" s="4"/>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="6">
+      <c r="C2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="7">
         <v>46240.0</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="7">
         <v>46241.0</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="7">
         <v>46242.0</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="6">
+      <c r="G2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="7">
         <v>46244.0</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="7">
         <v>46245.0</v>
       </c>
-      <c r="J2" s="6">
+      <c r="J2" s="7">
         <v>46246.0</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="7">
         <v>46247.0</v>
       </c>
-      <c r="L2" s="6">
+      <c r="L2" s="7">
         <v>46248.0</v>
       </c>
-      <c r="M2" s="6">
+      <c r="M2" s="7">
         <v>46249.0</v>
       </c>
-      <c r="N2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="O2" s="6">
+      <c r="N2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="O2" s="7">
         <v>46251.0</v>
       </c>
-      <c r="P2" s="6">
+      <c r="P2" s="7">
         <v>46252.0</v>
       </c>
-      <c r="Q2" s="6">
+      <c r="Q2" s="7">
         <v>46253.0</v>
       </c>
-      <c r="R2" s="6">
+      <c r="R2" s="7">
         <v>46254.0</v>
       </c>
-      <c r="S2" s="6">
+      <c r="S2" s="7">
         <v>46255.0</v>
       </c>
-      <c r="T2" s="5" t="s">
-        <v>9</v>
+      <c r="T2" s="6" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3"/>
-      <c r="B3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="A3" s="4"/>
+      <c r="B3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3"/>
-      <c r="S3" s="3"/>
-      <c r="T3" s="3"/>
+      <c r="C3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4"/>
+      <c r="T3" s="4"/>
     </row>
     <row r="4">
-      <c r="A4" s="3"/>
-      <c r="B4" s="4" t="s">
+      <c r="A4" s="4"/>
+      <c r="B4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="4"/>
+      <c r="T4" s="4"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4"/>
+      <c r="B5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3"/>
-      <c r="S4" s="3"/>
-      <c r="T4" s="3"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="3"/>
-      <c r="B5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
-      <c r="S5" s="3"/>
-      <c r="T5" s="3"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4"/>
+      <c r="S5" s="4"/>
+      <c r="T5" s="4"/>
     </row>
     <row r="6">
-      <c r="A6" s="3"/>
-      <c r="B6" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="4" t="s">
+      <c r="A6" s="4"/>
+      <c r="B6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
-      <c r="S6" s="3"/>
-      <c r="T6" s="3"/>
+      <c r="C6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="4"/>
+      <c r="S6" s="4"/>
+      <c r="T6" s="4"/>
     </row>
     <row r="7">
-      <c r="A7" s="3"/>
-      <c r="B7" s="4" t="s">
+      <c r="A7" s="4"/>
+      <c r="B7" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4"/>
+      <c r="S7" s="4"/>
+      <c r="T7" s="4"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4"/>
+      <c r="B8" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="4"/>
+      <c r="S8" s="4"/>
+      <c r="T8" s="4"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4"/>
+      <c r="B9" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
-      <c r="S7" s="3"/>
-      <c r="T7" s="3"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3"/>
-      <c r="B8" s="4" t="s">
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4"/>
+      <c r="S9" s="4"/>
+      <c r="T9" s="4"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4"/>
+      <c r="B10" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4"/>
+      <c r="S10" s="4"/>
+      <c r="T10" s="4"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="4"/>
+      <c r="S11" s="4"/>
+      <c r="T11" s="4"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4"/>
+      <c r="B12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="4"/>
+      <c r="O12" s="4"/>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4"/>
+      <c r="S12" s="4"/>
+      <c r="T12" s="4"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4"/>
+      <c r="B13" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="4"/>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="4"/>
+      <c r="S13" s="4"/>
+      <c r="T13" s="4"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4"/>
+      <c r="B14" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="4"/>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="4"/>
+      <c r="S14" s="4"/>
+      <c r="T14" s="4"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4"/>
+      <c r="B15" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="4"/>
+      <c r="N15" s="4"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="4"/>
+      <c r="Q15" s="4"/>
+      <c r="R15" s="4"/>
+      <c r="S15" s="4"/>
+      <c r="T15" s="4"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7"/>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="3"/>
-      <c r="S8" s="3"/>
-      <c r="T8" s="3"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3"/>
-      <c r="B9" s="4" t="s">
+    </row>
+    <row r="17">
+      <c r="B17" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
-      <c r="S9" s="3"/>
-      <c r="T9" s="3"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="3"/>
-      <c r="B10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="3"/>
-      <c r="S10" s="3"/>
-      <c r="T10" s="3"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="3"/>
-      <c r="S11" s="3"/>
-      <c r="T11" s="3"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3"/>
-      <c r="B12" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3"/>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="3"/>
-      <c r="S12" s="3"/>
-      <c r="T12" s="3"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3"/>
-      <c r="B13" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
-      <c r="S13" s="3"/>
-      <c r="T13" s="3"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3"/>
-      <c r="B14" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
-      <c r="P14" s="3"/>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="3"/>
-      <c r="S14" s="3"/>
-      <c r="T14" s="3"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3"/>
-      <c r="B15" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="3"/>
-      <c r="P15" s="3"/>
-      <c r="Q15" s="3"/>
-      <c r="R15" s="3"/>
-      <c r="S15" s="3"/>
-      <c r="T15" s="3"/>
-    </row>
-    <row r="16">
-      <c r="B16" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>20</v>
-      </c>
     </row>
     <row r="21">
-      <c r="B21" s="9" t="s">
-        <v>31</v>
+      <c r="B21" s="10" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="9" t="s">
-        <v>32</v>
+      <c r="B39" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="9" t="s">
-        <v>33</v>
+      <c r="B40" s="10" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="9" t="s">
-        <v>34</v>
+      <c r="A46" s="10" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="9">
+      <c r="A47" s="10">
         <v>1.0</v>
       </c>
-      <c r="B47" s="10" t="s">
-        <v>35</v>
+      <c r="B47" s="11" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="11" t="s">
-        <v>36</v>
+      <c r="B48" s="12" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E49" s="9" t="s">
+      <c r="B49" s="12" t="s">
         <v>38</v>
       </c>
+      <c r="E49" s="10" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="50">
-      <c r="B50" s="9" t="s">
+      <c r="B50" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="E50" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="E50" s="9" t="s">
-        <v>38</v>
-      </c>
     </row>
     <row r="51">
-      <c r="B51" s="9" t="s">
-        <v>40</v>
+      <c r="B51" s="10" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="9" t="s">
-        <v>41</v>
+      <c r="B52" s="10" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="E1"/>
+  </hyperlinks>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Project Plan.xlsx
+++ b/Project Plan.xlsx
@@ -3,7 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Version 2" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Version 1" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="46">
   <si>
     <t>Project Plan</t>
   </si>
@@ -37,7 +38,25 @@
     </r>
   </si>
   <si>
-    <t>milestone 1: component and page content added</t>
+    <r>
+      <rPr>
+        <rFont val="Calibri, sans-serif"/>
+        <b/>
+        <color rgb="FF000000"/>
+        <sz val="18.0"/>
+      </rPr>
+      <t xml:space="preserve">Project Github link: </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Calibri, sans-serif"/>
+        <b/>
+        <color rgb="FF1155CC"/>
+        <sz val="18.0"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/chaumdh/project-1-submission</t>
+    </r>
   </si>
   <si>
     <t>milestone 2: complete either your components or your page</t>
@@ -70,7 +89,7 @@
     <t>Chau</t>
   </si>
   <si>
-    <t>header - page tile image and title text</t>
+    <t>header - page title image and title text</t>
   </si>
   <si>
     <t>Everyone</t>
@@ -106,12 +125,18 @@
     <t>Melany</t>
   </si>
   <si>
+    <t>header - transparent at 1200px</t>
+  </si>
+  <si>
     <t>remaining content of page (wiouth header, footer, or awards)</t>
   </si>
   <si>
     <t>sign-in</t>
   </si>
   <si>
+    <t>footer - 2</t>
+  </si>
+  <si>
     <t>about</t>
   </si>
   <si>
@@ -140,6 +165,9 @@
   </si>
   <si>
     <t>Minimum 1 HTML table to display tabular data.</t>
+  </si>
+  <si>
+    <t>remaining content of page (without header, footer, or awards)</t>
   </si>
   <si>
     <t>Featured a simple VUE component within the site.</t>
@@ -214,7 +242,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -225,6 +253,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFA4C2F4"/>
         <bgColor rgb="FFA4C2F4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93C47D"/>
+        <bgColor rgb="FF93C47D"/>
       </patternFill>
     </fill>
     <fill>
@@ -265,7 +299,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -294,10 +328,17 @@
     <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="5" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -312,6 +353,10 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -543,9 +588,575 @@
       <c r="H1" s="4"/>
       <c r="I1" s="4"/>
       <c r="J1" s="4"/>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="S1" s="4"/>
+      <c r="T1" s="4"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="7">
+        <v>46240.0</v>
+      </c>
+      <c r="E2" s="7">
+        <v>46241.0</v>
+      </c>
+      <c r="F2" s="7">
+        <v>46242.0</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="7">
+        <v>46244.0</v>
+      </c>
+      <c r="I2" s="7">
+        <v>46245.0</v>
+      </c>
+      <c r="J2" s="7">
+        <v>46246.0</v>
+      </c>
+      <c r="K2" s="7">
+        <v>46247.0</v>
+      </c>
+      <c r="L2" s="7">
+        <v>46248.0</v>
+      </c>
+      <c r="M2" s="7">
+        <v>46249.0</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="O2" s="7">
+        <v>46251.0</v>
+      </c>
+      <c r="P2" s="7">
+        <v>46252.0</v>
+      </c>
+      <c r="Q2" s="7">
+        <v>46253.0</v>
+      </c>
+      <c r="R2" s="7">
+        <v>46254.0</v>
+      </c>
+      <c r="S2" s="7">
+        <v>46255.0</v>
+      </c>
+      <c r="T2" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9"/>
+      <c r="B3" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="11"/>
+      <c r="V3" s="11"/>
+      <c r="W3" s="11"/>
+      <c r="X3" s="11"/>
+      <c r="Y3" s="11"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4"/>
+      <c r="B4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="4"/>
+      <c r="T4" s="4"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="9"/>
+      <c r="B5" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="9"/>
+      <c r="U5" s="11"/>
+      <c r="V5" s="11"/>
+      <c r="W5" s="11"/>
+      <c r="X5" s="11"/>
+      <c r="Y5" s="11"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4"/>
+      <c r="B6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="4"/>
+      <c r="S6" s="4"/>
+      <c r="T6" s="4"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4"/>
+      <c r="B7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4"/>
+      <c r="S7" s="4"/>
+      <c r="T7" s="4"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4"/>
+      <c r="B8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="4"/>
+      <c r="S8" s="4"/>
+      <c r="T8" s="4"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4"/>
+      <c r="B9" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="12"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4"/>
+      <c r="S9" s="4"/>
+      <c r="T9" s="4"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4"/>
+      <c r="B10" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4"/>
+      <c r="S10" s="4"/>
+      <c r="T10" s="4"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="9"/>
+      <c r="B11" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="9"/>
+      <c r="O11" s="9"/>
+      <c r="P11" s="9"/>
+      <c r="Q11" s="9"/>
+      <c r="R11" s="9"/>
+      <c r="S11" s="9"/>
+      <c r="T11" s="9"/>
+      <c r="U11" s="11"/>
+      <c r="V11" s="11"/>
+      <c r="W11" s="11"/>
+      <c r="X11" s="11"/>
+      <c r="Y11" s="11"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="4"/>
+      <c r="O12" s="4"/>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4"/>
+      <c r="S12" s="4"/>
+      <c r="T12" s="4"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4"/>
+      <c r="B13" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="4"/>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="4"/>
+      <c r="S13" s="4"/>
+      <c r="T13" s="4"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4"/>
+      <c r="B14" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="4"/>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="4"/>
+      <c r="S14" s="4"/>
+      <c r="T14" s="4"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4"/>
+      <c r="B15" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="4"/>
+      <c r="N15" s="4"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="4"/>
+      <c r="Q15" s="4"/>
+      <c r="R15" s="4"/>
+      <c r="S15" s="4"/>
+      <c r="T15" s="4"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4"/>
+      <c r="B16" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="4"/>
+      <c r="N16" s="4"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="4"/>
+      <c r="Q16" s="4"/>
+      <c r="R16" s="4"/>
+      <c r="S16" s="4"/>
+      <c r="T16" s="4"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="B48" s="14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="15" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="E50" s="13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E51" s="13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="E1"/>
+  </hyperlinks>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="2" max="2" width="39.5"/>
+    <col customWidth="1" min="3" max="3" width="19.75"/>
+    <col customWidth="1" min="7" max="7" width="21.38"/>
+    <col customWidth="1" min="11" max="11" width="28.75"/>
+    <col customWidth="1" min="14" max="14" width="45.75"/>
+    <col customWidth="1" min="18" max="18" width="14.38"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
       <c r="L1" s="4"/>
       <c r="M1" s="4"/>
       <c r="N1" s="5" t="s">
@@ -766,12 +1377,12 @@
       <c r="G8" s="8"/>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
       <c r="R8" s="4"/>
@@ -851,7 +1462,7 @@
     <row r="12">
       <c r="A12" s="4"/>
       <c r="B12" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
@@ -875,7 +1486,7 @@
     <row r="13">
       <c r="A13" s="4"/>
       <c r="B13" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
@@ -898,8 +1509,8 @@
     </row>
     <row r="14">
       <c r="A14" s="4"/>
-      <c r="B14" s="10" t="s">
-        <v>27</v>
+      <c r="B14" s="13" t="s">
+        <v>29</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>24</v>
@@ -924,8 +1535,8 @@
     </row>
     <row r="15">
       <c r="A15" s="4"/>
-      <c r="B15" s="10" t="s">
-        <v>28</v>
+      <c r="B15" s="13" t="s">
+        <v>30</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>17</v>
@@ -949,86 +1560,86 @@
       <c r="T15" s="4"/>
     </row>
     <row r="16">
-      <c r="B16" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" s="10" t="s">
+      <c r="B16" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="13" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" s="10" t="s">
+      <c r="B17" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="13" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" s="10" t="s">
+      <c r="B18" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="13" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="10" t="s">
-        <v>32</v>
+      <c r="B21" s="13" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="10" t="s">
-        <v>33</v>
+      <c r="B39" s="13" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="10" t="s">
-        <v>34</v>
+      <c r="B40" s="13" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="10" t="s">
-        <v>35</v>
+      <c r="A46" s="13" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="10">
+      <c r="A47" s="13">
         <v>1.0</v>
       </c>
-      <c r="B47" s="11" t="s">
-        <v>36</v>
+      <c r="B47" s="14" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="12" t="s">
-        <v>37</v>
+      <c r="B48" s="15" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="E49" s="10" t="s">
-        <v>39</v>
+      <c r="B49" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="E49" s="13" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="E50" s="10" t="s">
-        <v>39</v>
+      <c r="B50" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E50" s="13" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="10" t="s">
-        <v>41</v>
+      <c r="B51" s="13" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="10" t="s">
-        <v>42</v>
+      <c r="B52" s="13" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
